--- a/Rekap_PROC_LMO.xlsx
+++ b/Rekap_PROC_LMO.xlsx
@@ -6,14 +6,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15750" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROC INTI LMO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROC UT LMO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROC DOWN LMO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROC HULU LMO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROC INTI LMO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROC UT LMO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROC DOWN LMO" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'PROC INTI LMO'!$B$2:$S$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'PROC UT LMO'!$B$2:$S$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'PROC DOWN LMO'!$B$2:$S$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'PROC HULU LMO'!$B$2:$S$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'PROC INTI LMO'!$B$2:$S$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'PROC UT LMO'!$B$2:$S$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'PROC DOWN LMO'!$B$2:$S$22</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -212,12 +214,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00F3F7F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F7F9"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -964,6 +966,816 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B2:S26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" style="1" min="2" max="2"/>
+    <col width="65" customWidth="1" style="1" min="3" max="3"/>
+    <col width="15" customWidth="1" style="1" min="4" max="10"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" style="1" min="11" max="13"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" style="1" min="14" max="17"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="25" customHeight="1">
+      <c r="B2" s="51" t="inlineStr">
+        <is>
+          <t>HASIL ANALISIS ISU PENTING BERDASARKAN PROSES HULU LMO
+Kontribusi Pareto ≥80% per kategori dampak</t>
+        </is>
+      </c>
+      <c r="C2" s="34" t="n"/>
+      <c r="D2" s="34" t="n"/>
+      <c r="E2" s="34" t="n"/>
+      <c r="F2" s="34" t="n"/>
+      <c r="G2" s="34" t="n"/>
+      <c r="H2" s="34" t="n"/>
+      <c r="I2" s="34" t="n"/>
+      <c r="J2" s="34" t="n"/>
+      <c r="K2" s="34" t="n"/>
+      <c r="L2" s="34" t="n"/>
+      <c r="M2" s="34" t="n"/>
+      <c r="N2" s="34" t="n"/>
+      <c r="O2" s="34" t="n"/>
+      <c r="P2" s="34" t="n"/>
+      <c r="Q2" s="34" t="n"/>
+      <c r="R2" s="34" t="n"/>
+      <c r="S2" s="35" t="n"/>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="37" t="n"/>
+      <c r="D3" s="37" t="n"/>
+      <c r="E3" s="37" t="n"/>
+      <c r="F3" s="37" t="n"/>
+      <c r="G3" s="37" t="n"/>
+      <c r="H3" s="37" t="n"/>
+      <c r="I3" s="37" t="n"/>
+      <c r="J3" s="37" t="n"/>
+      <c r="K3" s="37" t="n"/>
+      <c r="L3" s="37" t="n"/>
+      <c r="M3" s="37" t="n"/>
+      <c r="N3" s="37" t="n"/>
+      <c r="O3" s="37" t="n"/>
+      <c r="P3" s="37" t="n"/>
+      <c r="Q3" s="37" t="n"/>
+      <c r="R3" s="37" t="n"/>
+      <c r="S3" s="38" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Unit Proses</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Proses</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>GWP</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>ODP</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>POFP</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>ABF</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>ABN</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>ETP Terra</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>ETP Fresh</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="inlineStr">
+        <is>
+          <t>ETP Marine</t>
+        </is>
+      </c>
+      <c r="N5" s="22" t="inlineStr">
+        <is>
+          <t>HTC</t>
+        </is>
+      </c>
+      <c r="O5" s="22" t="inlineStr">
+        <is>
+          <t>HTN</t>
+        </is>
+      </c>
+      <c r="P5" s="22" t="inlineStr">
+        <is>
+          <t>WSF</t>
+        </is>
+      </c>
+      <c r="Q5" s="22" t="inlineStr">
+        <is>
+          <t>LUC</t>
+        </is>
+      </c>
+      <c r="R5" s="22" t="inlineStr">
+        <is>
+          <t>CEN</t>
+        </is>
+      </c>
+      <c r="S5" s="22" t="inlineStr">
+        <is>
+          <t>CED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="39" t="n"/>
+      <c r="C6" s="39" t="n"/>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>kg CO2-eq</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>kg CFC-11 eq</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>kg SO2 eq</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>kg PO4--- eq</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>kg C2H4 eq</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>kg Sb eq</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="N6" s="22" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t>kg 1,4-DCB</t>
+        </is>
+      </c>
+      <c r="P6" s="22" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>m2a crop eq</t>
+        </is>
+      </c>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="S6" s="22" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="23" customHeight="1">
+      <c r="B7" s="40" t="n"/>
+      <c r="C7" s="40" t="n"/>
+      <c r="D7" s="40" t="n"/>
+      <c r="E7" s="40" t="n"/>
+      <c r="F7" s="40" t="n"/>
+      <c r="G7" s="40" t="n"/>
+      <c r="H7" s="40" t="n"/>
+      <c r="I7" s="40" t="n"/>
+      <c r="J7" s="40" t="n"/>
+      <c r="K7" s="40" t="n"/>
+      <c r="L7" s="40" t="n"/>
+      <c r="M7" s="40" t="n"/>
+      <c r="N7" s="40" t="n"/>
+      <c r="O7" s="40" t="n"/>
+      <c r="P7" s="40" t="n"/>
+      <c r="Q7" s="40" t="n"/>
+      <c r="R7" s="40" t="n"/>
+      <c r="S7" s="40" t="n"/>
+    </row>
+    <row r="9" ht="23" customHeight="1">
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>Proses HULU — kategori di kolom; nilai dampak di atas, kontribusi di bawah</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="n"/>
+      <c r="D9" s="42" t="n"/>
+      <c r="E9" s="42" t="n"/>
+      <c r="F9" s="42" t="n"/>
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="42" t="n"/>
+      <c r="I9" s="42" t="n"/>
+      <c r="J9" s="42" t="n"/>
+      <c r="K9" s="42" t="n"/>
+      <c r="L9" s="42" t="n"/>
+      <c r="M9" s="42" t="n"/>
+      <c r="N9" s="42" t="n"/>
+      <c r="O9" s="42" t="n"/>
+      <c r="P9" s="42" t="n"/>
+      <c r="Q9" s="42" t="n"/>
+      <c r="R9" s="42" t="n"/>
+      <c r="S9" s="43" t="n"/>
+    </row>
+    <row r="10" ht="31" customHeight="1">
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>1. Supporting Material Production and Transportation</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>Ammonium nitrate {RoW}| market for ammonium nitrate | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n">
+        <v>1.442779e-05</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>3.9334904</v>
+      </c>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n">
+        <v>0.0031838035</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.010640494</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.23483628</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0.5604662</v>
+      </c>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n">
+        <v>12.0605218923</v>
+      </c>
+      <c r="S10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n">
+        <v>0.3847825103082436</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.2625620161180831</v>
+      </c>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n">
+        <v>0.1335421330251496</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0.209450025122994</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0.5882188007214937</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0.1732867859945162</v>
+      </c>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n">
+        <v>0.06516423244233004</v>
+      </c>
+      <c r="S11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="31" customHeight="1">
+      <c r="B12" s="39" t="n"/>
+      <c r="C12" s="53" t="inlineStr">
+        <is>
+          <t>Textile, knit cotton {GLO}| market for | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n">
+        <v>0.003622227</v>
+      </c>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n">
+        <v>1.7474544</v>
+      </c>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="B13" s="39" t="n"/>
+      <c r="C13" s="40" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n">
+        <v>0.2045388054744977</v>
+      </c>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n">
+        <v>0.5402837078274759</v>
+      </c>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="31" customHeight="1">
+      <c r="B14" s="39" t="n"/>
+      <c r="C14" s="53" t="inlineStr">
+        <is>
+          <t>Battery, lead acid, rechargeable, stationary {GLO}| market for battery, lead acid, rechargeable, stationary | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n">
+        <v>2.2301595e-06</v>
+      </c>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="B15" s="40" t="n"/>
+      <c r="C15" s="40" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n">
+        <v>0.05947732610453696</v>
+      </c>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="31" customHeight="1">
+      <c r="B16" s="53" t="inlineStr">
+        <is>
+          <t>2. Land Clearing</t>
+        </is>
+      </c>
+      <c r="C16" s="53" t="inlineStr">
+        <is>
+          <t>2. Land Clearing</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n">
+        <v>8.717156599999999</v>
+      </c>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="B17" s="40" t="n"/>
+      <c r="C17" s="40" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n">
+        <v>0.7040975609519693</v>
+      </c>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="31" customHeight="1">
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>5. Overburden Removal</t>
+        </is>
+      </c>
+      <c r="C18" s="53" t="inlineStr">
+        <is>
+          <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>6.1744842</v>
+      </c>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n">
+        <v>0.018281569</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.0033777732</v>
+      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n">
+        <v>1.5346169e-05</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>5.303712</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0.0092230647</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0.0065122655</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0.019564875</v>
+      </c>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n">
+        <v>0.7866089000000001</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>3.3151813</v>
+      </c>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n">
+        <v>121.766652266</v>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="B19" s="39" t="n"/>
+      <c r="C19" s="40" t="n"/>
+      <c r="D19" s="3" t="n">
+        <v>0.2551598752517306</v>
+      </c>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n">
+        <v>0.6243285628889425</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.2976499671003325</v>
+      </c>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n">
+        <v>0.4092752550067993</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.3540248415579381</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.5208051943050523</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0.2731518530261345</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0.3851196721015244</v>
+      </c>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n">
+        <v>0.2432063309360704</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>0.2677720700169111</v>
+      </c>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="n">
+        <v>0.9606605991727885</v>
+      </c>
+    </row>
+    <row r="20" ht="31" customHeight="1">
+      <c r="B20" s="39" t="n"/>
+      <c r="C20" s="53" t="inlineStr">
+        <is>
+          <t>Diesel {RoW}| diesel production, petroleum refinery operation | Cut-off, S</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n">
+        <v>1.7699786e-06</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.013417967</v>
+      </c>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n">
+        <v>134.33865</v>
+      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n">
+        <v>4.0573518</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0.003127234</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0.010385131</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.010814617</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0.21025261</v>
+      </c>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n">
+        <v>142.92772500147</v>
+      </c>
+      <c r="S20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="B21" s="39" t="n"/>
+      <c r="C21" s="40" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n">
+        <v>0.8795875767735185</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.1061641755711976</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n">
+        <v>0.80263807332902</v>
+      </c>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n">
+        <v>0.2708298128065428</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.1765876922675568</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0.4355961495379992</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0.2128775038400997</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0.5266415312947553</v>
+      </c>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n">
+        <v>0.7722531062603157</v>
+      </c>
+      <c r="S21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="31" customHeight="1">
+      <c r="B22" s="39" t="n"/>
+      <c r="C22" s="53" t="inlineStr">
+        <is>
+          <t>5. Overburden Removal</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>14.445036</v>
+      </c>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n">
+        <v>0.092357495</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0.0063456453</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.0068795884</v>
+      </c>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="B23" s="40" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="3" t="n">
+        <v>0.5969395117679234</v>
+      </c>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n">
+        <v>0.730740902440437</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.216708292967194</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.6062305370069929</v>
+      </c>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+    </row>
+    <row r="25" ht="27" customHeight="1">
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>Unit proses di luar Pareto: 3. Top Soil Removal; 4. Drilling and Blasting</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>Sumber: SimaPro LMO.xlsx / PROC HULU LMO. Kontribusi bertanda mengikuti SimaPro; kumulatif arah neto ada di workbook gabungan / Audit Pareto. CEN/CED diagregasi; ETP terpisah.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="B9:S9"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="B2:S3"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B26:S26"/>
+    <mergeCell ref="B25:S25"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="F6:F7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1838,7 +2650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2723,7 +3535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Rekap_PROC_LMO.xlsx
+++ b/Rekap_PROC_LMO.xlsx
@@ -1265,7 +1265,9 @@
           <t>Ammonium nitrate {RoW}| market for ammonium nitrate | Cut-off, S</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>1.3259296</v>
+      </c>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
@@ -1299,7 +1301,9 @@
     <row r="11" ht="21" customHeight="1">
       <c r="B11" s="39" t="n"/>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>0.07160300752919138</v>
+      </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
@@ -1493,9 +1497,7 @@
           <t>Palm oil, crude {MY}| palm oil mill operation | Cut-off, S</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>6.1744842</v>
-      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n">
@@ -1535,9 +1537,7 @@
     <row r="19" ht="21" customHeight="1">
       <c r="B19" s="39" t="n"/>
       <c r="C19" s="40" t="n"/>
-      <c r="D19" s="3" t="n">
-        <v>0.2551598752517306</v>
-      </c>
+      <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n">
@@ -1690,7 +1690,7 @@
       <c r="B23" s="40" t="n"/>
       <c r="C23" s="40" t="n"/>
       <c r="D23" s="3" t="n">
-        <v>0.5969395117679234</v>
+        <v>0.7800625474138602</v>
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n">
